--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -1,33 +1,130 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+  </si>
+  <si>
+    <t>ADOLFO'S VICAR, C.A.</t>
+  </si>
+  <si>
+    <t>13590</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>RECEPCION</t>
+  </si>
+  <si>
+    <t>Josbeiker A. Rojas</t>
+  </si>
+  <si>
+    <t>Genesis Tovar Recibidora</t>
+  </si>
+  <si>
+    <t>DOCUMENTACIÓN ERRÓNEA</t>
+  </si>
+  <si>
+    <t>ERROR DE KG EN TARA.</t>
+  </si>
+  <si>
+    <t>TIPO B</t>
+  </si>
+  <si>
+    <t>TIPO C</t>
+  </si>
+  <si>
+    <t>Recibidora saca cuenta mal sumando una tara mas</t>
+  </si>
+  <si>
+    <t>00004591</t>
+  </si>
+  <si>
+    <t>COBRO</t>
+  </si>
+  <si>
+    <t>HIST_20260501_0</t>
+  </si>
+  <si>
+    <t>20260504130808</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +143,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,144 +437,119 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HIST_20260501_0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MORA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>024721</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Josbeiker A. Rojas</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TIPO B</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Documentacion erronea</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>24721</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2">
         <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3">
+        <v>4.66</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -94,19 +94,25 @@
     <t>TIPO C</t>
   </si>
   <si>
-    <t>Recibidora saca cuenta mal sumando una tara mas</t>
+    <t>SIN OBSERVACIONES, CAMBIO</t>
+  </si>
+  <si>
+    <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
   </si>
   <si>
     <t>00004591</t>
   </si>
   <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
     <t>COBRO</t>
   </si>
   <si>
-    <t>HIST_20260501_0</t>
-  </si>
-  <si>
-    <t>20260504130808</t>
+    <t>20260501_0</t>
+  </si>
+  <si>
+    <t>HIST_20260504162247</t>
   </si>
 </sst>
 </file>
@@ -495,6 +501,9 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
       <c r="F2" t="s">
         <v>20</v>
       </c>
@@ -504,11 +513,20 @@
       <c r="H2" t="s">
         <v>24</v>
       </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
       <c r="K2">
         <v>0</v>
       </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -537,19 +555,19 @@
         <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3">
         <v>4.66</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -55,6 +55,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>FOTO_INCIDENCIA</t>
+  </si>
+  <si>
     <t>MORA</t>
   </si>
   <si>
@@ -64,7 +67,10 @@
     <t>ADOLFO'S VICAR, C.A.</t>
   </si>
   <si>
-    <t>13590</t>
+    <t>FABRICA DE HIELO EL OSO, C.A</t>
+  </si>
+  <si>
+    <t>40812</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -73,6 +79,9 @@
     <t>2026-05-04</t>
   </si>
   <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
@@ -82,6 +91,9 @@
     <t>Genesis Tovar Recibidora</t>
   </si>
   <si>
+    <t>Yosmary A. Villanueva</t>
+  </si>
+  <si>
     <t>DOCUMENTACIÓN ERRÓNEA</t>
   </si>
   <si>
@@ -100,7 +112,10 @@
     <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
   </si>
   <si>
-    <t>00004591</t>
+    <t>Se coloco la documentacion al reves y se pide volver a subirla correctamente</t>
+  </si>
+  <si>
+    <t>SIN_FOTO</t>
   </si>
   <si>
     <t>NINGUNA</t>
@@ -113,6 +128,9 @@
   </si>
   <si>
     <t>HIST_20260504162247</t>
+  </si>
+  <si>
+    <t>ID_20260505113534</t>
   </si>
 </sst>
 </file>
@@ -444,10 +462,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,34 +505,37 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>24721</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -523,51 +544,92 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>13590</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
         <v>29</v>
       </c>
-      <c r="M2" t="s">
+      <c r="I3" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
       </c>
       <c r="J3">
         <v>4.66</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3">
+        <v>4591</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="I4" t="s">
         <v>32</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -1,157 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>FOTO_INCIDENCIA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
-  </si>
-  <si>
-    <t>ADOLFO'S VICAR, C.A.</t>
-  </si>
-  <si>
-    <t>FABRICA DE HIELO EL OSO, C.A</t>
-  </si>
-  <si>
-    <t>40812</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>Josbeiker A. Rojas</t>
-  </si>
-  <si>
-    <t>Genesis Tovar Recibidora</t>
-  </si>
-  <si>
-    <t>Yosmary A. Villanueva</t>
-  </si>
-  <si>
-    <t>DOCUMENTACIÓN ERRÓNEA</t>
-  </si>
-  <si>
-    <t>ERROR DE KG EN TARA.</t>
-  </si>
-  <si>
-    <t>TIPO B</t>
-  </si>
-  <si>
-    <t>TIPO C</t>
-  </si>
-  <si>
-    <t>SIN OBSERVACIONES, CAMBIO</t>
-  </si>
-  <si>
-    <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
-  </si>
-  <si>
-    <t>Se coloco la documentacion al reves y se pide volver a subirla correctamente</t>
-  </si>
-  <si>
-    <t>SIN_FOTO</t>
-  </si>
-  <si>
-    <t>NINGUNA</t>
-  </si>
-  <si>
-    <t>COBRO</t>
-  </si>
-  <si>
-    <t>20260501_0</t>
-  </si>
-  <si>
-    <t>HIST_20260504162247</t>
-  </si>
-  <si>
-    <t>ID_20260505113534</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -166,14 +51,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,175 +414,271 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24721</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Josbeiker A. Rojas</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SIN OBSERVACIONES, CAMBIO</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>20260501_0</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>24721</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>13590</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Genesis Tovar Recibidora</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4591</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>HIST_20260504162247</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FABRICA DE HIELO EL OSO, C.A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>40812</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yosmary A. Villanueva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Se coloco la documentacion al reves y se pide volver a subirla correctamente</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>13590</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3">
-        <v>4.66</v>
-      </c>
-      <c r="K3">
-        <v>4591</v>
-      </c>
-      <c r="L3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" t="s">
-        <v>38</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260505113534</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -1,12 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,12 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +548,7 @@
           <t>20260501_0</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -599,7 +594,7 @@
           <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" t="n">
         <v>4.66</v>
       </c>
       <c r="K3" t="n">
@@ -615,6 +610,7 @@
           <t>HIST_20260504162247</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -627,10 +623,8 @@
           <t>FABRICA DE HIELO EL OSO, C.A</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>40812</t>
-        </is>
+      <c r="C4" t="n">
+        <v>40812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -680,8 +674,75 @@
           <t>ID_20260505113534</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>32533</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yosmary A. Villanueva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Producto SKU no pertenece a la devolucion</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260507101310</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +555,6 @@
           <t>20260501_0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -594,7 +600,7 @@
           <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>4.66</v>
       </c>
       <c r="K3" t="n">
@@ -610,7 +616,6 @@
           <t>HIST_20260504162247</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -674,7 +679,6 @@
           <t>ID_20260505113534</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -740,7 +744,6 @@
           <t>ID_20260507101310</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +548,7 @@
           <t>20260501_0</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,7 +594,7 @@
           <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" t="n">
         <v>4.66</v>
       </c>
       <c r="K3" t="n">
@@ -616,6 +610,7 @@
           <t>HIST_20260504162247</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,6 +674,7 @@
           <t>ID_20260505113534</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -691,10 +687,8 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>32533</t>
-        </is>
+      <c r="C5" t="n">
+        <v>32533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -744,6 +738,73 @@
           <t>ID_20260507101310</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SUPERMERCADOS LUXOR, C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>008107</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>YOSMARY A. VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>El producto Sku no pertenece a la transferencia y se cargara en otro documento</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260512155141</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +555,6 @@
           <t>20260501_0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -594,7 +600,7 @@
           <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>4.66</v>
       </c>
       <c r="K3" t="n">
@@ -610,7 +616,6 @@
           <t>HIST_20260504162247</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -674,7 +679,6 @@
           <t>ID_20260505113534</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -738,7 +742,6 @@
           <t>ID_20260507101310</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -804,7 +807,6 @@
           <t>ID_20260512155141</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +548,7 @@
           <t>20260501_0</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,7 +594,7 @@
           <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" t="n">
         <v>4.66</v>
       </c>
       <c r="K3" t="n">
@@ -616,6 +610,7 @@
           <t>HIST_20260504162247</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,6 +674,7 @@
           <t>ID_20260505113534</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -742,6 +738,7 @@
           <t>ID_20260507101310</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -754,10 +751,8 @@
           <t>SUPERMERCADOS LUXOR, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>008107</t>
-        </is>
+      <c r="C6" t="n">
+        <v>8107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -807,6 +802,139 @@
           <t>ID_20260512155141</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INVERSIONES LACTEAS SAN SIMON, C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D00013997</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JOHANA C. GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Error en SKU duplicado LAC3364</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260513161711</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INVERSIONES LACTEAS SAN SIMON, C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D00013997</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JOHANA C. GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falta un producto fiscalizado en el error de sku duplicado no se agrego </t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260513162128</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +555,6 @@
           <t>20260501_0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -594,7 +600,7 @@
           <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>4.66</v>
       </c>
       <c r="K3" t="n">
@@ -610,7 +616,6 @@
           <t>HIST_20260504162247</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -674,7 +679,6 @@
           <t>ID_20260505113534</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -738,7 +742,6 @@
           <t>ID_20260507101310</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -802,7 +805,6 @@
           <t>ID_20260512155141</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -868,7 +870,6 @@
           <t>ID_20260513161711</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -934,7 +935,6 @@
           <t>ID_20260513162128</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,11 +534,13 @@
           <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
         </is>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" t="n">
         <v>4.66</v>
       </c>
-      <c r="K2" t="n">
-        <v>4591</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -557,6 +552,7 @@
           <t>HIST_20260504162247</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -622,6 +618,7 @@
           <t>ID_20260505113534</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -687,6 +684,7 @@
           <t>ID_20260507101310</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -752,6 +750,7 @@
           <t>ID_20260512155141</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -817,6 +816,7 @@
           <t>ID_20260513161711</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -882,6 +882,7 @@
           <t>ID_20260513162128</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -947,6 +948,7 @@
           <t>ID_20260522125728</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1082,6 +1084,7 @@
           <t>ID_20260528113732</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1148,6 +1151,7 @@
           <t>ID_20260529133231</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1213,6 +1217,7 @@
           <t>20260501_0</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,17 +496,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADOLFO'S VICAR, C.A.</t>
+          <t>FABRICA DE HIELO EL OSO, C.A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>40812</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,26 +516,26 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Genesis Tovar Recibidora</t>
+          <t>Yosmary A. Villanueva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ERROR DE KG EN TARA.</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TIPO C</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
+          <t>Se coloco la documentacion al reves y se pide volver a subirla correctamente</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -544,12 +544,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>HIST_20260504162247</t>
+          <t>ID_20260505113534</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -562,22 +562,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FABRICA DE HIELO EL OSO, C.A</t>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40812</t>
+          <t>32533</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO C</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Se coloco la documentacion al reves y se pide volver a subirla correctamente</t>
+          <t>Producto SKU no pertenece a la devolucion</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ID_20260505113534</t>
+          <t>ID_20260507101310</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -628,27 +628,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
+          <t>SUPERMERCADOS LUXOR, C.A.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32533</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DEVOLUCION</t>
+          <t>TRANSFERENCIA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yosmary A. Villanueva</t>
+          <t>YOSMARY A. VILLANUEVA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Producto SKU no pertenece a la devolucion</t>
+          <t>El producto Sku no pertenece a la transferencia y se cargara en otro documento</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260507101310</t>
+          <t>ID_20260512155141</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -694,42 +694,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SUPERMERCADOS LUXOR, C.A.</t>
+          <t>INVERSIONES LACTEAS SAN SIMON, C.A.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>D00013997</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TRANSFERENCIA</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>YOSMARY A. VILLANUEVA</t>
+          <t>JOHANA C. GUTIERREZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO C</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>El producto Sku no pertenece a la transferencia y se cargara en otro documento</t>
+          <t>Error en SKU duplicado LAC3364</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260512155141</t>
+          <t>ID_20260513161711</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -785,17 +785,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PRODUCTO O SKU DUPLICADO.</t>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO C</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Error en SKU duplicado LAC3364</t>
+          <t xml:space="preserve">Falta un producto fiscalizado en el error de sku duplicado no se agrego </t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260513161711</t>
+          <t>ID_20260513162128</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -826,17 +826,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INVERSIONES LACTEAS SAN SIMON, C.A.</t>
+          <t>C.P.A BEJUMA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>D00013997</t>
+          <t>0000074632</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -846,22 +846,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JOHANA C. GUTIERREZ</t>
+          <t>HEDI J. ROA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+          <t>DOCUMENTO NO LEGIBLE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TIPO C</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falta un producto fiscalizado en el error de sku duplicado no se agrego </t>
+          <t>Documento no cuadrado bien la foto y no se ven bien los numeros de factura</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ID_20260513162128</t>
+          <t>ID_20260522125728</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -892,17 +892,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C.P.A BEJUMA</t>
+          <t>PRODUCTOS ALIMEX C.A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0000074632</t>
+          <t>0040706</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HEDI J. ROA</t>
+          <t>JOSBEIKER A. ROJAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DOCUMENTO NO LEGIBLE</t>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Documento no cuadrado bien la foto y no se ven bien los numeros de factura</t>
+          <t>Sale cortada el domumento al dorso y no se ven las firmas faltantes</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -945,10 +945,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ID_20260522125728</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>ID_20260528112305</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>INC_112305_0.png</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -958,12 +962,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PRODUCTOS ALIMEX C.A</t>
+          <t>FRUMIX,C.A.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0040706</t>
+          <t>00009930</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -993,7 +997,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sale cortada el domumento al dorso y no se ven las firmas faltantes</t>
+          <t>falta firma de de pcp y recibidora en documento al dorso</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1011,14 +1015,10 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ID_20260528112305</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>INC_112305_0.png</t>
-        </is>
-      </c>
+          <t>ID_20260528113732</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FRUMIX,C.A.</t>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>00009930</t>
+          <t>026450</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1053,17 +1053,18 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>falta firma de de pcp y recibidora en documento al dorso</t>
+          <t xml:space="preserve">Erro en SKU duplicado RFR7543
+</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1081,7 +1082,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ID_20260528113732</t>
+          <t>ID_20260529133231</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1099,12 +1100,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>026450</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1114,12 +1115,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JOSBEIKER A. ROJAS</t>
+          <t>Josbeiker A. Rojas</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PRODUCTO O SKU DUPLICADO.</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1129,8 +1130,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erro en SKU duplicado RFR7543
-</t>
+          <t>Error en documentacion</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1148,76 +1148,10 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ID_20260529133231</t>
+          <t>20260501_0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MORA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>24721</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Josbeiker A. Rojas</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>TIPO B</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Error en documentacion</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>SIN_FOTO</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>20260501_0</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -552,7 +552,6 @@
           <t>ID_20260505113534</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -618,7 +617,6 @@
           <t>ID_20260507101310</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -684,7 +682,6 @@
           <t>ID_20260512155141</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -750,7 +747,6 @@
           <t>ID_20260513161711</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -816,7 +812,6 @@
           <t>ID_20260513162128</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -882,7 +877,6 @@
           <t>ID_20260522125728</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1018,7 +1012,6 @@
           <t>ID_20260528113732</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1085,7 +1078,6 @@
           <t>ID_20260529133231</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1151,7 +1143,6 @@
           <t>20260501_0</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/MORA.xlsx
+++ b/cuadros/MAYO/MORA.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1148,71 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>20260501_0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13590</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Genesis Tovar Recibidora</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Error en tara al sacar la cuenta se conto solo 1 cesta</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>COB_115033_0.jpeg</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260603115033</t>
         </is>
       </c>
     </row>
